--- a/artfynd/A 32793-2025 artfynd.xlsx
+++ b/artfynd/A 32793-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129395994</v>
       </c>
       <c r="B2" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129406905</v>
+        <v>129410982</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560134</v>
+        <v>559966</v>
       </c>
       <c r="R4" t="n">
-        <v>7063629</v>
+        <v>7063789</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,19 +957,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:49</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,12 +979,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1113,7 +1108,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129406877</v>
+        <v>129411008</v>
       </c>
       <c r="B6" t="n">
         <v>79041</v>
@@ -1144,14 +1139,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560134</v>
+        <v>559922</v>
       </c>
       <c r="R6" t="n">
-        <v>7063639</v>
+        <v>7063790</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,19 +1176,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,22 +1193,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129410982</v>
+        <v>129406877</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,34 +1216,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559966</v>
+        <v>560134</v>
       </c>
       <c r="R7" t="n">
-        <v>7063789</v>
+        <v>7063639</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,14 +1273,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,19 +1300,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129411008</v>
+        <v>129406905</v>
       </c>
       <c r="B8" t="n">
         <v>79041</v>
@@ -1353,14 +1343,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559922</v>
+        <v>560134</v>
       </c>
       <c r="R8" t="n">
-        <v>7063790</v>
+        <v>7063629</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,9 +1380,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1407,12 +1407,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129407377</v>
+        <v>129410983</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,34 +1848,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560226</v>
+        <v>559933</v>
       </c>
       <c r="R13" t="n">
-        <v>7063565</v>
+        <v>7063772</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,19 +1905,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>16:08</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>16:08</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1932,12 +1927,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2051,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129410983</v>
+        <v>129407377</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2062,34 +2057,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559933</v>
+        <v>560226</v>
       </c>
       <c r="R15" t="n">
-        <v>7063772</v>
+        <v>7063565</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2119,14 +2114,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2141,19 +2141,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129407859</v>
+        <v>129407762</v>
       </c>
       <c r="B16" t="n">
         <v>79041</v>
@@ -2188,13 +2188,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560055</v>
+        <v>560107</v>
       </c>
       <c r="R16" t="n">
-        <v>7063757</v>
+        <v>7063737</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,7 +2260,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129407762</v>
+        <v>129407859</v>
       </c>
       <c r="B17" t="n">
         <v>79041</v>
@@ -2295,13 +2295,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560107</v>
+        <v>560055</v>
       </c>
       <c r="R17" t="n">
-        <v>7063737</v>
+        <v>7063757</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2706,7 +2706,7 @@
         <v>129410997</v>
       </c>
       <c r="B21" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2805,45 +2805,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129410980</v>
+        <v>129407633</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>98706</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559994</v>
+        <v>560193</v>
       </c>
       <c r="R22" t="n">
-        <v>7063702</v>
+        <v>7063641</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2873,14 +2877,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2895,61 +2904,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129407633</v>
+        <v>129410980</v>
       </c>
       <c r="B23" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560193</v>
+        <v>559994</v>
       </c>
       <c r="R23" t="n">
-        <v>7063641</v>
+        <v>7063702</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2979,19 +2984,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>16:20</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3006,22 +3006,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129406824</v>
+        <v>129406681</v>
       </c>
       <c r="B24" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,34 +3029,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560095</v>
+        <v>560028</v>
       </c>
       <c r="R24" t="n">
-        <v>7063636</v>
+        <v>7063663</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3088,7 +3093,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3098,7 +3103,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3125,10 +3135,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129406681</v>
+        <v>129406722</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,39 +3146,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560028</v>
+        <v>560046</v>
       </c>
       <c r="R25" t="n">
-        <v>7063663</v>
+        <v>7063665</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3200,7 +3205,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3210,12 +3215,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3242,10 +3242,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129406722</v>
+        <v>129406824</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3253,34 +3253,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560046</v>
+        <v>560095</v>
       </c>
       <c r="R26" t="n">
-        <v>7063665</v>
+        <v>7063636</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3312,7 +3312,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 32793-2025 artfynd.xlsx
+++ b/artfynd/A 32793-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129395994</v>
       </c>
       <c r="B2" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129406836</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129410982</v>
+        <v>129406905</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559966</v>
+        <v>560134</v>
       </c>
       <c r="R4" t="n">
-        <v>7063789</v>
+        <v>7063629</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,14 +957,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,22 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129406697</v>
+        <v>129411008</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,39 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560040</v>
+        <v>559922</v>
       </c>
       <c r="R5" t="n">
-        <v>7063656</v>
+        <v>7063790</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,24 +1064,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,22 +1081,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129411008</v>
+        <v>129406877</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,14 +1124,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559922</v>
+        <v>560134</v>
       </c>
       <c r="R6" t="n">
-        <v>7063790</v>
+        <v>7063639</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,9 +1161,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,22 +1188,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129406877</v>
+        <v>129410982</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,34 +1211,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560134</v>
+        <v>559966</v>
       </c>
       <c r="R7" t="n">
-        <v>7063639</v>
+        <v>7063789</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,19 +1268,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:48</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1300,22 +1290,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129406905</v>
+        <v>129406697</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,34 +1313,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560134</v>
+        <v>560040</v>
       </c>
       <c r="R8" t="n">
-        <v>7063629</v>
+        <v>7063656</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1377,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1392,7 +1387,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,7 +1422,7 @@
         <v>129408046</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>129411007</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1623,32 +1623,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129407893</v>
+        <v>129407794</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>91507</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>560059</v>
+        <v>560102</v>
       </c>
       <c r="R11" t="n">
-        <v>7063756</v>
+        <v>7063742</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,32 +1730,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129407794</v>
+        <v>129407893</v>
       </c>
       <c r="B12" t="n">
-        <v>91504</v>
+        <v>79043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560102</v>
+        <v>560059</v>
       </c>
       <c r="R12" t="n">
-        <v>7063742</v>
+        <v>7063756</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129410983</v>
+        <v>129407377</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,34 +1848,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559933</v>
+        <v>560226</v>
       </c>
       <c r="R13" t="n">
-        <v>7063772</v>
+        <v>7063565</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,14 +1905,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1927,12 +1932,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1942,7 +1947,7 @@
         <v>129407592</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129407377</v>
+        <v>129410983</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2057,34 +2062,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560226</v>
+        <v>559933</v>
       </c>
       <c r="R15" t="n">
-        <v>7063565</v>
+        <v>7063772</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2114,19 +2119,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>16:08</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>16:08</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2141,22 +2141,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129407762</v>
+        <v>129407859</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2188,13 +2188,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560107</v>
+        <v>560055</v>
       </c>
       <c r="R16" t="n">
-        <v>7063737</v>
+        <v>7063757</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,10 +2260,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129407859</v>
+        <v>129407762</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2295,13 +2295,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560055</v>
+        <v>560107</v>
       </c>
       <c r="R17" t="n">
-        <v>7063757</v>
+        <v>7063737</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2599,7 +2599,7 @@
         <v>129407821</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129410997</v>
+        <v>129407633</v>
       </c>
       <c r="B21" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2733,19 +2733,19 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559930</v>
+        <v>560193</v>
       </c>
       <c r="R21" t="n">
-        <v>7063777</v>
+        <v>7063641</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2775,40 +2775,49 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129407633</v>
+        <v>129410997</v>
       </c>
       <c r="B22" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2835,19 +2844,19 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560193</v>
+        <v>559930</v>
       </c>
       <c r="R22" t="n">
-        <v>7063641</v>
+        <v>7063777</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,39 +2886,30 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3018,10 +3018,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129406681</v>
+        <v>129406824</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>80148</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,39 +3029,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560028</v>
+        <v>560095</v>
       </c>
       <c r="R24" t="n">
-        <v>7063663</v>
+        <v>7063636</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3093,7 +3088,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3103,12 +3098,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3138,7 +3128,7 @@
         <v>129406722</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3242,10 +3232,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129406824</v>
+        <v>129406681</v>
       </c>
       <c r="B26" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3253,34 +3243,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560095</v>
+        <v>560028</v>
       </c>
       <c r="R26" t="n">
-        <v>7063636</v>
+        <v>7063663</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3312,7 +3307,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3322,7 +3317,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3453,7 +3453,7 @@
         <v>129407124</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>129406968</v>
       </c>
       <c r="B29" t="n">
-        <v>80175</v>
+        <v>80177</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 32793-2025 artfynd.xlsx
+++ b/artfynd/A 32793-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129395994</v>
       </c>
       <c r="B2" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129406836</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129406905</v>
+        <v>129411008</v>
       </c>
       <c r="B4" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,14 +920,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560134</v>
+        <v>559922</v>
       </c>
       <c r="R4" t="n">
-        <v>7063629</v>
+        <v>7063790</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,19 +957,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129411008</v>
+        <v>129406877</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,14 +1017,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559922</v>
+        <v>560134</v>
       </c>
       <c r="R5" t="n">
-        <v>7063790</v>
+        <v>7063639</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,9 +1054,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,22 +1081,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129406877</v>
+        <v>129406905</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>560134</v>
       </c>
       <c r="R6" t="n">
-        <v>7063639</v>
+        <v>7063629</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1422,7 +1422,7 @@
         <v>129408046</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>129411007</v>
       </c>
       <c r="B10" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>129407794</v>
       </c>
       <c r="B11" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>129407893</v>
       </c>
       <c r="B12" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1837,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129407377</v>
+        <v>129410983</v>
       </c>
       <c r="B13" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,34 +1848,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560226</v>
+        <v>559933</v>
       </c>
       <c r="R13" t="n">
-        <v>7063565</v>
+        <v>7063772</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,19 +1905,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>16:08</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>16:08</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1932,22 +1927,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129407592</v>
+        <v>129407377</v>
       </c>
       <c r="B14" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560233</v>
+        <v>560226</v>
       </c>
       <c r="R14" t="n">
-        <v>7063609</v>
+        <v>7063565</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2014,7 +2009,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2024,7 +2019,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129410983</v>
+        <v>129407592</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2062,34 +2057,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559933</v>
+        <v>560233</v>
       </c>
       <c r="R15" t="n">
-        <v>7063772</v>
+        <v>7063609</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2119,14 +2114,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2141,12 +2141,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2156,7 +2156,7 @@
         <v>129407859</v>
       </c>
       <c r="B16" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>129407762</v>
       </c>
       <c r="B17" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2367,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129406811</v>
+        <v>129407351</v>
       </c>
       <c r="B18" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2378,16 +2378,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2403,14 +2403,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560083</v>
+        <v>560249</v>
       </c>
       <c r="R18" t="n">
-        <v>7063653</v>
+        <v>7063529</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2452,7 +2452,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129407351</v>
+        <v>129406811</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2490,16 +2495,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2515,14 +2520,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560249</v>
+        <v>560083</v>
       </c>
       <c r="R19" t="n">
-        <v>7063529</v>
+        <v>7063653</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2554,7 +2559,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2564,12 +2569,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2599,7 +2599,7 @@
         <v>129407821</v>
       </c>
       <c r="B20" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2703,49 +2703,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129407633</v>
+        <v>129410980</v>
       </c>
       <c r="B21" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560193</v>
+        <v>559994</v>
       </c>
       <c r="R21" t="n">
-        <v>7063641</v>
+        <v>7063702</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2775,19 +2771,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>16:20</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2802,12 +2793,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2817,7 +2808,7 @@
         <v>129410997</v>
       </c>
       <c r="B22" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2916,45 +2907,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129410980</v>
+        <v>129407633</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559994</v>
+        <v>560193</v>
       </c>
       <c r="R23" t="n">
-        <v>7063702</v>
+        <v>7063641</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2984,14 +2979,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3006,12 +3006,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3021,7 +3021,7 @@
         <v>129406824</v>
       </c>
       <c r="B24" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>129406722</v>
       </c>
       <c r="B25" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>129407124</v>
       </c>
       <c r="B28" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>129406968</v>
       </c>
       <c r="B29" t="n">
-        <v>80177</v>
+        <v>80178</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 32793-2025 artfynd.xlsx
+++ b/artfynd/A 32793-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129395994</v>
       </c>
       <c r="B2" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129411008</v>
+        <v>129410982</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559922</v>
+        <v>559966</v>
       </c>
       <c r="R4" t="n">
-        <v>7063790</v>
+        <v>7063789</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129406877</v>
+        <v>129406697</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,34 +1002,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560134</v>
+        <v>560040</v>
       </c>
       <c r="R5" t="n">
-        <v>7063639</v>
+        <v>7063656</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1066,7 +1076,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1200,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129410982</v>
+        <v>129411008</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559966</v>
+        <v>559922</v>
       </c>
       <c r="R7" t="n">
-        <v>7063789</v>
+        <v>7063790</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,11 +1286,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129406697</v>
+        <v>129406877</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1313,39 +1323,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560040</v>
+        <v>560134</v>
       </c>
       <c r="R8" t="n">
-        <v>7063656</v>
+        <v>7063639</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,7 +1382,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1387,12 +1392,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:39</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1626,7 +1626,7 @@
         <v>129407794</v>
       </c>
       <c r="B11" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1837,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129410983</v>
+        <v>129407377</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,34 +1848,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559933</v>
+        <v>560226</v>
       </c>
       <c r="R13" t="n">
-        <v>7063772</v>
+        <v>7063565</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,14 +1905,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1927,19 +1932,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129407377</v>
+        <v>129407592</v>
       </c>
       <c r="B14" t="n">
         <v>79044</v>
@@ -1974,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560226</v>
+        <v>560233</v>
       </c>
       <c r="R14" t="n">
-        <v>7063565</v>
+        <v>7063609</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2009,7 +2014,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2019,7 +2024,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129407592</v>
+        <v>129410983</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2057,34 +2062,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560233</v>
+        <v>559933</v>
       </c>
       <c r="R15" t="n">
-        <v>7063609</v>
+        <v>7063772</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2114,19 +2119,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>16:17</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2141,12 +2141,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2703,45 +2703,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129410980</v>
+        <v>129410997</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>98716</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559994</v>
+        <v>559930</v>
       </c>
       <c r="R21" t="n">
-        <v>7063702</v>
+        <v>7063777</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2776,17 +2780,13 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2805,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129410997</v>
+        <v>129407633</v>
       </c>
       <c r="B22" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2835,19 +2835,19 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559930</v>
+        <v>560193</v>
       </c>
       <c r="R22" t="n">
-        <v>7063777</v>
+        <v>7063641</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,79 +2877,84 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129407633</v>
+        <v>129410980</v>
       </c>
       <c r="B23" t="n">
-        <v>98712</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560193</v>
+        <v>559994</v>
       </c>
       <c r="R23" t="n">
-        <v>7063641</v>
+        <v>7063702</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2979,19 +2984,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>16:20</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3006,12 +3006,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 32793-2025 artfynd.xlsx
+++ b/artfynd/A 32793-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129395994</v>
       </c>
       <c r="B2" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129410982</v>
+        <v>129406905</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559966</v>
+        <v>560134</v>
       </c>
       <c r="R4" t="n">
-        <v>7063789</v>
+        <v>7063629</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,14 +957,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,22 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129406697</v>
+        <v>129411008</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,39 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560040</v>
+        <v>559922</v>
       </c>
       <c r="R5" t="n">
-        <v>7063656</v>
+        <v>7063790</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,24 +1064,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,19 +1081,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129406905</v>
+        <v>129406877</v>
       </c>
       <c r="B6" t="n">
         <v>79044</v>
@@ -1146,7 +1131,7 @@
         <v>560134</v>
       </c>
       <c r="R6" t="n">
-        <v>7063629</v>
+        <v>7063639</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129411008</v>
+        <v>129410982</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559922</v>
+        <v>559966</v>
       </c>
       <c r="R7" t="n">
-        <v>7063790</v>
+        <v>7063789</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1271,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129406877</v>
+        <v>129406697</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,34 +1313,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560134</v>
+        <v>560040</v>
       </c>
       <c r="R8" t="n">
-        <v>7063639</v>
+        <v>7063656</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1377,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1392,7 +1387,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1626,7 +1626,7 @@
         <v>129407794</v>
       </c>
       <c r="B11" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2703,49 +2703,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129410997</v>
+        <v>129410980</v>
       </c>
       <c r="B21" t="n">
-        <v>98716</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559930</v>
+        <v>559994</v>
       </c>
       <c r="R21" t="n">
-        <v>7063777</v>
+        <v>7063702</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2780,13 +2776,17 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2805,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129407633</v>
+        <v>129410997</v>
       </c>
       <c r="B22" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2835,19 +2835,19 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560193</v>
+        <v>559930</v>
       </c>
       <c r="R22" t="n">
-        <v>7063641</v>
+        <v>7063777</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,84 +2877,79 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129410980</v>
+        <v>129407633</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559994</v>
+        <v>560193</v>
       </c>
       <c r="R23" t="n">
-        <v>7063702</v>
+        <v>7063641</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2984,14 +2979,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3006,12 +3006,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 32793-2025 artfynd.xlsx
+++ b/artfynd/A 32793-2025 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129406905</v>
+        <v>129410982</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560134</v>
+        <v>559966</v>
       </c>
       <c r="R4" t="n">
-        <v>7063629</v>
+        <v>7063789</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,19 +957,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:49</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,22 +979,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129411008</v>
+        <v>129406697</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +1002,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559922</v>
+        <v>560040</v>
       </c>
       <c r="R5" t="n">
-        <v>7063790</v>
+        <v>7063656</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,9 +1064,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,19 +1096,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129406877</v>
+        <v>129406905</v>
       </c>
       <c r="B6" t="n">
         <v>79044</v>
@@ -1131,7 +1146,7 @@
         <v>560134</v>
       </c>
       <c r="R6" t="n">
-        <v>7063639</v>
+        <v>7063629</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1173,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129410982</v>
+        <v>129411008</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559966</v>
+        <v>559922</v>
       </c>
       <c r="R7" t="n">
-        <v>7063789</v>
+        <v>7063790</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,11 +1286,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129406697</v>
+        <v>129406877</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1313,39 +1323,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560040</v>
+        <v>560134</v>
       </c>
       <c r="R8" t="n">
-        <v>7063656</v>
+        <v>7063639</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,7 +1382,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1387,12 +1392,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:39</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1623,32 +1623,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129407794</v>
+        <v>129407893</v>
       </c>
       <c r="B11" t="n">
-        <v>91514</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>560102</v>
+        <v>560059</v>
       </c>
       <c r="R11" t="n">
-        <v>7063742</v>
+        <v>7063756</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,32 +1730,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129407893</v>
+        <v>129407794</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>91514</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560059</v>
+        <v>560102</v>
       </c>
       <c r="R12" t="n">
-        <v>7063756</v>
+        <v>7063742</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -3018,10 +3018,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129406824</v>
+        <v>129406722</v>
       </c>
       <c r="B24" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,34 +3029,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560095</v>
+        <v>560046</v>
       </c>
       <c r="R24" t="n">
-        <v>7063636</v>
+        <v>7063665</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3125,10 +3125,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129406722</v>
+        <v>129406824</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,34 +3136,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560046</v>
+        <v>560095</v>
       </c>
       <c r="R25" t="n">
-        <v>7063665</v>
+        <v>7063636</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 32793-2025 artfynd.xlsx
+++ b/artfynd/A 32793-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129410982</v>
+        <v>129406905</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559966</v>
+        <v>560134</v>
       </c>
       <c r="R4" t="n">
-        <v>7063789</v>
+        <v>7063629</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,14 +957,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,22 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129406697</v>
+        <v>129411008</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,39 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560040</v>
+        <v>559922</v>
       </c>
       <c r="R5" t="n">
-        <v>7063656</v>
+        <v>7063790</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,24 +1064,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,19 +1081,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129406905</v>
+        <v>129406877</v>
       </c>
       <c r="B6" t="n">
         <v>79044</v>
@@ -1146,7 +1131,7 @@
         <v>560134</v>
       </c>
       <c r="R6" t="n">
-        <v>7063629</v>
+        <v>7063639</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129411008</v>
+        <v>129410982</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559922</v>
+        <v>559966</v>
       </c>
       <c r="R7" t="n">
-        <v>7063790</v>
+        <v>7063789</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1271,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129406877</v>
+        <v>129406697</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,34 +1313,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560134</v>
+        <v>560040</v>
       </c>
       <c r="R8" t="n">
-        <v>7063639</v>
+        <v>7063656</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1377,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1392,7 +1387,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2703,45 +2703,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129410980</v>
+        <v>129410997</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559994</v>
+        <v>559930</v>
       </c>
       <c r="R21" t="n">
-        <v>7063702</v>
+        <v>7063777</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2776,17 +2780,13 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2805,7 +2805,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129410997</v>
+        <v>129407633</v>
       </c>
       <c r="B22" t="n">
         <v>98724</v>
@@ -2835,19 +2835,19 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559930</v>
+        <v>560193</v>
       </c>
       <c r="R22" t="n">
-        <v>7063777</v>
+        <v>7063641</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,79 +2877,84 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129407633</v>
+        <v>129410980</v>
       </c>
       <c r="B23" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560193</v>
+        <v>559994</v>
       </c>
       <c r="R23" t="n">
-        <v>7063641</v>
+        <v>7063702</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2979,19 +2984,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>16:20</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3006,12 +3006,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3662,6 +3662,1393 @@
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129559957</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91550</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Spångmyran, Spångmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>559912</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7063780</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129559998</v>
+      </c>
+      <c r="B31" t="n">
+        <v>88950</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>510</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Spångmyran, Spångmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>559907</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7063773</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129561840</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91848</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>658</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Spångmyran, Spångmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>560074</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7063724</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129561392</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91848</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>658</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Spångmyran, Spångmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>560043</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7063681</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129561598</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91550</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Spångmyran, Spångmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>560048</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7063683</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129561826</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91550</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Spångmyran, Spångmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>560071</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7063709</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129561747</v>
+      </c>
+      <c r="B36" t="n">
+        <v>83012</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Spångmyran, Spångmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>560071</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7063717</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129561089</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91550</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Spångmyran, Spångmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>560043</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7063692</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129561632</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91550</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Spångmyran, Spångmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>560075</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7063677</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129561809</v>
+      </c>
+      <c r="B39" t="n">
+        <v>92003</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Spångmyran, Spångmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>560067</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7063707</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129559867</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Spångmyran, Spångmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>559918</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7063800</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129561092</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91848</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>658</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Spångmyran, Spångmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>560041</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7063693</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129562162</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Spångmyran, Spångmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>560041</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7063796</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129562154</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Spångmyran, Spångmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>560039</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7063789</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Gammalt bohål i fallen björk, 3.5 upp. 4cm diameter.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32793-2025 artfynd.xlsx
+++ b/artfynd/A 32793-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129395994</v>
       </c>
       <c r="B2" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129406905</v>
+        <v>129410982</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560134</v>
+        <v>559966</v>
       </c>
       <c r="R4" t="n">
-        <v>7063629</v>
+        <v>7063789</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,19 +957,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:49</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,22 +979,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129411008</v>
+        <v>129406697</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +1002,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559922</v>
+        <v>560040</v>
       </c>
       <c r="R5" t="n">
-        <v>7063790</v>
+        <v>7063656</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,9 +1064,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,19 +1096,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129406877</v>
+        <v>129406905</v>
       </c>
       <c r="B6" t="n">
         <v>79044</v>
@@ -1131,7 +1146,7 @@
         <v>560134</v>
       </c>
       <c r="R6" t="n">
-        <v>7063639</v>
+        <v>7063629</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1173,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129410982</v>
+        <v>129411008</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559966</v>
+        <v>559922</v>
       </c>
       <c r="R7" t="n">
-        <v>7063789</v>
+        <v>7063790</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,11 +1286,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129406697</v>
+        <v>129406877</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1313,39 +1323,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560040</v>
+        <v>560134</v>
       </c>
       <c r="R8" t="n">
-        <v>7063656</v>
+        <v>7063639</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,7 +1382,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1387,12 +1392,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:39</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1733,7 +1733,7 @@
         <v>129407794</v>
       </c>
       <c r="B12" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2703,49 +2703,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129410997</v>
+        <v>129410980</v>
       </c>
       <c r="B21" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559930</v>
+        <v>559994</v>
       </c>
       <c r="R21" t="n">
-        <v>7063777</v>
+        <v>7063702</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2780,13 +2776,17 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2805,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129407633</v>
+        <v>129410997</v>
       </c>
       <c r="B22" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2835,19 +2835,19 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560193</v>
+        <v>559930</v>
       </c>
       <c r="R22" t="n">
-        <v>7063641</v>
+        <v>7063777</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,84 +2877,79 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129410980</v>
+        <v>129407633</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559994</v>
+        <v>560193</v>
       </c>
       <c r="R23" t="n">
-        <v>7063702</v>
+        <v>7063641</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2984,14 +2979,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3006,22 +3006,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129406722</v>
+        <v>129406824</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,34 +3029,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560046</v>
+        <v>560095</v>
       </c>
       <c r="R24" t="n">
-        <v>7063665</v>
+        <v>7063636</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3125,10 +3125,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129406824</v>
+        <v>129406722</v>
       </c>
       <c r="B25" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,34 +3136,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560095</v>
+        <v>560046</v>
       </c>
       <c r="R25" t="n">
-        <v>7063636</v>
+        <v>7063665</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3667,7 +3667,7 @@
         <v>129559957</v>
       </c>
       <c r="B30" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>129559998</v>
       </c>
       <c r="B31" t="n">
-        <v>88950</v>
+        <v>88952</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3858,10 +3858,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129561840</v>
+        <v>129561826</v>
       </c>
       <c r="B32" t="n">
-        <v>91848</v>
+        <v>91553</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3869,21 +3869,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560074</v>
+        <v>560071</v>
       </c>
       <c r="R32" t="n">
-        <v>7063724</v>
+        <v>7063709</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3958,7 +3958,7 @@
         <v>129561392</v>
       </c>
       <c r="B33" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4052,10 +4052,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129561598</v>
+        <v>129561840</v>
       </c>
       <c r="B34" t="n">
-        <v>91550</v>
+        <v>91851</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4063,21 +4063,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4087,10 +4087,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560048</v>
+        <v>560074</v>
       </c>
       <c r="R34" t="n">
-        <v>7063683</v>
+        <v>7063724</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4149,10 +4149,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129561826</v>
+        <v>129561598</v>
       </c>
       <c r="B35" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560071</v>
+        <v>560048</v>
       </c>
       <c r="R35" t="n">
-        <v>7063709</v>
+        <v>7063683</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4346,7 +4346,7 @@
         <v>129561089</v>
       </c>
       <c r="B37" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>129561632</v>
       </c>
       <c r="B38" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>129561809</v>
       </c>
       <c r="B39" t="n">
-        <v>92003</v>
+        <v>92006</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>129561092</v>
       </c>
       <c r="B41" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 32793-2025 artfynd.xlsx
+++ b/artfynd/A 32793-2025 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129410982</v>
+        <v>129406905</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559966</v>
+        <v>560134</v>
       </c>
       <c r="R4" t="n">
-        <v>7063789</v>
+        <v>7063629</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,14 +957,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,19 +984,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129406697</v>
+        <v>129410982</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1020,21 +1025,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560040</v>
+        <v>559966</v>
       </c>
       <c r="R5" t="n">
-        <v>7063656</v>
+        <v>7063789</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,24 +1064,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,22 +1086,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129406905</v>
+        <v>129406697</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,34 +1109,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560134</v>
+        <v>560040</v>
       </c>
       <c r="R6" t="n">
-        <v>7063629</v>
+        <v>7063656</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1183,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1623,32 +1623,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129407893</v>
+        <v>129407794</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>91517</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>560059</v>
+        <v>560102</v>
       </c>
       <c r="R11" t="n">
-        <v>7063756</v>
+        <v>7063742</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,32 +1730,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129407794</v>
+        <v>129407893</v>
       </c>
       <c r="B12" t="n">
-        <v>91517</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560102</v>
+        <v>560059</v>
       </c>
       <c r="R12" t="n">
-        <v>7063742</v>
+        <v>7063756</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -3955,10 +3955,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129561392</v>
+        <v>129561598</v>
       </c>
       <c r="B33" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3966,21 +3966,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3990,10 +3990,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560043</v>
+        <v>560048</v>
       </c>
       <c r="R33" t="n">
-        <v>7063681</v>
+        <v>7063683</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4052,7 +4052,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129561840</v>
+        <v>129561392</v>
       </c>
       <c r="B34" t="n">
         <v>91851</v>
@@ -4087,10 +4087,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560074</v>
+        <v>560043</v>
       </c>
       <c r="R34" t="n">
-        <v>7063724</v>
+        <v>7063681</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4149,10 +4149,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129561598</v>
+        <v>129561840</v>
       </c>
       <c r="B35" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4160,21 +4160,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560048</v>
+        <v>560074</v>
       </c>
       <c r="R35" t="n">
-        <v>7063683</v>
+        <v>7063724</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>

--- a/artfynd/A 32793-2025 artfynd.xlsx
+++ b/artfynd/A 32793-2025 artfynd.xlsx
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129406905</v>
+        <v>129411008</v>
       </c>
       <c r="B4" t="n">
         <v>79044</v>
@@ -920,14 +920,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560134</v>
+        <v>559922</v>
       </c>
       <c r="R4" t="n">
-        <v>7063629</v>
+        <v>7063790</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,19 +957,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129410982</v>
+        <v>129406905</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559966</v>
+        <v>560134</v>
       </c>
       <c r="R5" t="n">
-        <v>7063789</v>
+        <v>7063629</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,14 +1054,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,22 +1081,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129406697</v>
+        <v>129406877</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,39 +1104,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560040</v>
+        <v>560134</v>
       </c>
       <c r="R6" t="n">
-        <v>7063656</v>
+        <v>7063639</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,12 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:39</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129411008</v>
+        <v>129410982</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559922</v>
+        <v>559966</v>
       </c>
       <c r="R7" t="n">
-        <v>7063790</v>
+        <v>7063789</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1271,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129406877</v>
+        <v>129406697</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,34 +1313,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560134</v>
+        <v>560040</v>
       </c>
       <c r="R8" t="n">
-        <v>7063639</v>
+        <v>7063656</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1377,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1392,7 +1387,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129408046</v>
+        <v>129411007</v>
       </c>
       <c r="B9" t="n">
         <v>79044</v>
@@ -1450,14 +1450,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560033</v>
+        <v>559954</v>
       </c>
       <c r="R9" t="n">
-        <v>7063815</v>
+        <v>7063768</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1487,19 +1487,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>16:42</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>16:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1514,19 +1504,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129411007</v>
+        <v>129408046</v>
       </c>
       <c r="B10" t="n">
         <v>79044</v>
@@ -1557,14 +1547,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559954</v>
+        <v>560033</v>
       </c>
       <c r="R10" t="n">
-        <v>7063768</v>
+        <v>7063815</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1594,9 +1584,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1611,12 +1611,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2367,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129407351</v>
+        <v>129406811</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2378,16 +2378,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2403,14 +2403,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560249</v>
+        <v>560083</v>
       </c>
       <c r="R18" t="n">
-        <v>7063529</v>
+        <v>7063653</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2452,12 +2452,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129406811</v>
+        <v>129407351</v>
       </c>
       <c r="B19" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2495,16 +2490,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2520,14 +2515,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560083</v>
+        <v>560249</v>
       </c>
       <c r="R19" t="n">
-        <v>7063653</v>
+        <v>7063529</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2559,7 +2554,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2569,7 +2564,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2703,45 +2703,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129410980</v>
+        <v>129410997</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559994</v>
+        <v>559930</v>
       </c>
       <c r="R21" t="n">
-        <v>7063702</v>
+        <v>7063777</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2776,17 +2780,13 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2805,7 +2805,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129410997</v>
+        <v>129407633</v>
       </c>
       <c r="B22" t="n">
         <v>98727</v>
@@ -2835,19 +2835,19 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559930</v>
+        <v>560193</v>
       </c>
       <c r="R22" t="n">
-        <v>7063777</v>
+        <v>7063641</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,79 +2877,84 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129407633</v>
+        <v>129410980</v>
       </c>
       <c r="B23" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560193</v>
+        <v>559994</v>
       </c>
       <c r="R23" t="n">
-        <v>7063641</v>
+        <v>7063702</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2979,19 +2984,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>16:20</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3006,22 +3006,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129406824</v>
+        <v>129406722</v>
       </c>
       <c r="B24" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,34 +3029,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560095</v>
+        <v>560046</v>
       </c>
       <c r="R24" t="n">
-        <v>7063636</v>
+        <v>7063665</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3125,10 +3125,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129406722</v>
+        <v>129406824</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,34 +3136,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560046</v>
+        <v>560095</v>
       </c>
       <c r="R25" t="n">
-        <v>7063665</v>
+        <v>7063636</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3858,10 +3858,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129561826</v>
+        <v>129561392</v>
       </c>
       <c r="B32" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3869,21 +3869,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560071</v>
+        <v>560043</v>
       </c>
       <c r="R32" t="n">
-        <v>7063709</v>
+        <v>7063681</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3955,10 +3955,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129561598</v>
+        <v>129561840</v>
       </c>
       <c r="B33" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3966,21 +3966,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3990,10 +3990,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560048</v>
+        <v>560074</v>
       </c>
       <c r="R33" t="n">
-        <v>7063683</v>
+        <v>7063724</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4052,10 +4052,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129561392</v>
+        <v>129561826</v>
       </c>
       <c r="B34" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4063,21 +4063,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4087,10 +4087,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560043</v>
+        <v>560071</v>
       </c>
       <c r="R34" t="n">
-        <v>7063681</v>
+        <v>7063709</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4149,10 +4149,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129561840</v>
+        <v>129561598</v>
       </c>
       <c r="B35" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4160,21 +4160,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560074</v>
+        <v>560048</v>
       </c>
       <c r="R35" t="n">
-        <v>7063724</v>
+        <v>7063683</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129561089</v>
+        <v>129561632</v>
       </c>
       <c r="B37" t="n">
         <v>91553</v>
@@ -4378,10 +4378,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560043</v>
+        <v>560075</v>
       </c>
       <c r="R37" t="n">
-        <v>7063692</v>
+        <v>7063677</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4440,7 +4440,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129561632</v>
+        <v>129561089</v>
       </c>
       <c r="B38" t="n">
         <v>91553</v>
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560075</v>
+        <v>560043</v>
       </c>
       <c r="R38" t="n">
-        <v>7063677</v>
+        <v>7063692</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>

--- a/artfynd/A 32793-2025 artfynd.xlsx
+++ b/artfynd/A 32793-2025 artfynd.xlsx
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129411008</v>
+        <v>129406905</v>
       </c>
       <c r="B4" t="n">
         <v>79044</v>
@@ -920,14 +920,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559922</v>
+        <v>560134</v>
       </c>
       <c r="R4" t="n">
-        <v>7063790</v>
+        <v>7063629</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,9 +957,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,19 +984,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129406905</v>
+        <v>129411008</v>
       </c>
       <c r="B5" t="n">
         <v>79044</v>
@@ -1017,14 +1027,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560134</v>
+        <v>559922</v>
       </c>
       <c r="R5" t="n">
-        <v>7063629</v>
+        <v>7063790</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,19 +1064,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,12 +1081,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1419,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129411007</v>
+        <v>129408046</v>
       </c>
       <c r="B9" t="n">
         <v>79044</v>
@@ -1450,14 +1450,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559954</v>
+        <v>560033</v>
       </c>
       <c r="R9" t="n">
-        <v>7063768</v>
+        <v>7063815</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1487,9 +1487,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1504,19 +1514,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129408046</v>
+        <v>129411007</v>
       </c>
       <c r="B10" t="n">
         <v>79044</v>
@@ -1547,14 +1557,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560033</v>
+        <v>559954</v>
       </c>
       <c r="R10" t="n">
-        <v>7063815</v>
+        <v>7063768</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1584,19 +1594,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>16:42</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>16:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1611,44 +1611,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129407794</v>
+        <v>129407893</v>
       </c>
       <c r="B11" t="n">
-        <v>91517</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>560102</v>
+        <v>560059</v>
       </c>
       <c r="R11" t="n">
-        <v>7063742</v>
+        <v>7063756</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,32 +1730,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129407893</v>
+        <v>129407794</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>91517</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560059</v>
+        <v>560102</v>
       </c>
       <c r="R12" t="n">
-        <v>7063756</v>
+        <v>7063742</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2703,49 +2703,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129410997</v>
+        <v>129410980</v>
       </c>
       <c r="B21" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559930</v>
+        <v>559994</v>
       </c>
       <c r="R21" t="n">
-        <v>7063777</v>
+        <v>7063702</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2780,13 +2776,17 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2805,7 +2805,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129407633</v>
+        <v>129410997</v>
       </c>
       <c r="B22" t="n">
         <v>98727</v>
@@ -2835,19 +2835,19 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560193</v>
+        <v>559930</v>
       </c>
       <c r="R22" t="n">
-        <v>7063641</v>
+        <v>7063777</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,84 +2877,79 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129410980</v>
+        <v>129407633</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559994</v>
+        <v>560193</v>
       </c>
       <c r="R23" t="n">
-        <v>7063702</v>
+        <v>7063641</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2984,14 +2979,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3006,12 +3006,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3858,7 +3858,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129561392</v>
+        <v>129561840</v>
       </c>
       <c r="B32" t="n">
         <v>91851</v>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560043</v>
+        <v>560074</v>
       </c>
       <c r="R32" t="n">
-        <v>7063681</v>
+        <v>7063724</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3955,7 +3955,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129561840</v>
+        <v>129561392</v>
       </c>
       <c r="B33" t="n">
         <v>91851</v>
@@ -3990,10 +3990,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560074</v>
+        <v>560043</v>
       </c>
       <c r="R33" t="n">
-        <v>7063724</v>
+        <v>7063681</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129561632</v>
+        <v>129561089</v>
       </c>
       <c r="B37" t="n">
         <v>91553</v>
@@ -4378,10 +4378,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560075</v>
+        <v>560043</v>
       </c>
       <c r="R37" t="n">
-        <v>7063677</v>
+        <v>7063692</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4440,7 +4440,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129561089</v>
+        <v>129561632</v>
       </c>
       <c r="B38" t="n">
         <v>91553</v>
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560043</v>
+        <v>560075</v>
       </c>
       <c r="R38" t="n">
-        <v>7063692</v>
+        <v>7063677</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>

--- a/artfynd/A 32793-2025 artfynd.xlsx
+++ b/artfynd/A 32793-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129411008</v>
+        <v>129406877</v>
       </c>
       <c r="B5" t="n">
         <v>79044</v>
@@ -1027,14 +1027,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559922</v>
+        <v>560134</v>
       </c>
       <c r="R5" t="n">
-        <v>7063790</v>
+        <v>7063639</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,9 +1064,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,22 +1091,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129406877</v>
+        <v>129410982</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,34 +1114,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560134</v>
+        <v>559966</v>
       </c>
       <c r="R6" t="n">
-        <v>7063639</v>
+        <v>7063789</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,19 +1171,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:48</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,19 +1193,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129410982</v>
+        <v>129406697</v>
       </c>
       <c r="B7" t="n">
         <v>57727</v>
@@ -1229,16 +1234,21 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559966</v>
+        <v>560040</v>
       </c>
       <c r="R7" t="n">
-        <v>7063789</v>
+        <v>7063656</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1268,14 +1278,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1290,22 +1310,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129406697</v>
+        <v>129411008</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1313,39 +1333,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560040</v>
+        <v>559922</v>
       </c>
       <c r="R8" t="n">
-        <v>7063656</v>
+        <v>7063790</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1375,24 +1390,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1407,12 +1407,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2367,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129406811</v>
+        <v>129407351</v>
       </c>
       <c r="B18" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2378,16 +2378,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2403,14 +2403,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560083</v>
+        <v>560249</v>
       </c>
       <c r="R18" t="n">
-        <v>7063653</v>
+        <v>7063529</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2452,7 +2452,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129407351</v>
+        <v>129406811</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2490,16 +2495,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2515,14 +2520,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560249</v>
+        <v>560083</v>
       </c>
       <c r="R19" t="n">
-        <v>7063529</v>
+        <v>7063653</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2554,7 +2559,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2564,12 +2569,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3018,10 +3018,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129406722</v>
+        <v>129406824</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,34 +3029,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560046</v>
+        <v>560095</v>
       </c>
       <c r="R24" t="n">
-        <v>7063665</v>
+        <v>7063636</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3125,10 +3125,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129406824</v>
+        <v>129406722</v>
       </c>
       <c r="B25" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,34 +3136,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560095</v>
+        <v>560046</v>
       </c>
       <c r="R25" t="n">
-        <v>7063636</v>
+        <v>7063665</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3858,10 +3858,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129561840</v>
+        <v>129561826</v>
       </c>
       <c r="B32" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3869,21 +3869,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560074</v>
+        <v>560071</v>
       </c>
       <c r="R32" t="n">
-        <v>7063724</v>
+        <v>7063709</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3955,10 +3955,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129561392</v>
+        <v>129561598</v>
       </c>
       <c r="B33" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3966,21 +3966,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3990,10 +3990,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560043</v>
+        <v>560048</v>
       </c>
       <c r="R33" t="n">
-        <v>7063681</v>
+        <v>7063683</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4052,10 +4052,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129561826</v>
+        <v>129561392</v>
       </c>
       <c r="B34" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4063,21 +4063,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4087,10 +4087,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560071</v>
+        <v>560043</v>
       </c>
       <c r="R34" t="n">
-        <v>7063709</v>
+        <v>7063681</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4149,10 +4149,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129561598</v>
+        <v>129561840</v>
       </c>
       <c r="B35" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4160,21 +4160,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560048</v>
+        <v>560074</v>
       </c>
       <c r="R35" t="n">
-        <v>7063683</v>
+        <v>7063724</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>

--- a/artfynd/A 32793-2025 artfynd.xlsx
+++ b/artfynd/A 32793-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129406877</v>
+        <v>129411008</v>
       </c>
       <c r="B5" t="n">
         <v>79044</v>
@@ -1027,14 +1027,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560134</v>
+        <v>559922</v>
       </c>
       <c r="R5" t="n">
-        <v>7063639</v>
+        <v>7063790</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,19 +1064,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,22 +1081,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129410982</v>
+        <v>129406877</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,34 +1104,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559966</v>
+        <v>560134</v>
       </c>
       <c r="R6" t="n">
-        <v>7063789</v>
+        <v>7063639</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1171,14 +1161,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,19 +1188,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129406697</v>
+        <v>129410982</v>
       </c>
       <c r="B7" t="n">
         <v>57727</v>
@@ -1234,21 +1229,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560040</v>
+        <v>559966</v>
       </c>
       <c r="R7" t="n">
-        <v>7063656</v>
+        <v>7063789</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1278,24 +1268,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,22 +1290,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129411008</v>
+        <v>129406697</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,34 +1313,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559922</v>
+        <v>560040</v>
       </c>
       <c r="R8" t="n">
-        <v>7063790</v>
+        <v>7063656</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,9 +1375,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1407,12 +1407,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2703,45 +2703,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129410980</v>
+        <v>129407633</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559994</v>
+        <v>560193</v>
       </c>
       <c r="R21" t="n">
-        <v>7063702</v>
+        <v>7063641</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2771,14 +2775,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2793,12 +2802,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2907,49 +2916,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129407633</v>
+        <v>129410980</v>
       </c>
       <c r="B23" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560193</v>
+        <v>559994</v>
       </c>
       <c r="R23" t="n">
-        <v>7063641</v>
+        <v>7063702</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2979,19 +2984,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>16:20</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3006,22 +3006,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129406824</v>
+        <v>129406681</v>
       </c>
       <c r="B24" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,34 +3029,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560095</v>
+        <v>560028</v>
       </c>
       <c r="R24" t="n">
-        <v>7063636</v>
+        <v>7063663</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3088,7 +3093,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3098,7 +3103,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3125,10 +3135,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129406722</v>
+        <v>129406824</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,34 +3146,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560046</v>
+        <v>560095</v>
       </c>
       <c r="R25" t="n">
-        <v>7063665</v>
+        <v>7063636</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3195,7 +3205,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3205,7 +3215,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3232,10 +3242,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129406681</v>
+        <v>129406722</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3243,39 +3253,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560028</v>
+        <v>560046</v>
       </c>
       <c r="R26" t="n">
-        <v>7063663</v>
+        <v>7063665</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3307,7 +3312,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3317,12 +3322,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3858,10 +3858,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129561826</v>
+        <v>129561392</v>
       </c>
       <c r="B32" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3869,21 +3869,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560071</v>
+        <v>560043</v>
       </c>
       <c r="R32" t="n">
-        <v>7063709</v>
+        <v>7063681</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3955,10 +3955,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129561598</v>
+        <v>129561840</v>
       </c>
       <c r="B33" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3966,21 +3966,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3990,10 +3990,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560048</v>
+        <v>560074</v>
       </c>
       <c r="R33" t="n">
-        <v>7063683</v>
+        <v>7063724</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4052,10 +4052,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129561392</v>
+        <v>129561826</v>
       </c>
       <c r="B34" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4063,21 +4063,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4087,10 +4087,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560043</v>
+        <v>560071</v>
       </c>
       <c r="R34" t="n">
-        <v>7063681</v>
+        <v>7063709</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4149,10 +4149,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129561840</v>
+        <v>129561598</v>
       </c>
       <c r="B35" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4160,21 +4160,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560074</v>
+        <v>560048</v>
       </c>
       <c r="R35" t="n">
-        <v>7063724</v>
+        <v>7063683</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>

--- a/artfynd/A 32793-2025 artfynd.xlsx
+++ b/artfynd/A 32793-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129395994</v>
       </c>
       <c r="B2" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129406836</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129406905</v>
+        <v>129411008</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,14 +920,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560134</v>
+        <v>559922</v>
       </c>
       <c r="R4" t="n">
-        <v>7063629</v>
+        <v>7063790</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,19 +957,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129411008</v>
+        <v>129406877</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,14 +1017,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559922</v>
+        <v>560134</v>
       </c>
       <c r="R5" t="n">
-        <v>7063790</v>
+        <v>7063639</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,9 +1054,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,22 +1081,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129406877</v>
+        <v>129406905</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>560134</v>
       </c>
       <c r="R6" t="n">
-        <v>7063639</v>
+        <v>7063629</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,7 +1203,7 @@
         <v>129410982</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>129406697</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>129408046</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>129411007</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1623,32 +1623,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129407893</v>
+        <v>129407794</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>91545</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>560059</v>
+        <v>560102</v>
       </c>
       <c r="R11" t="n">
-        <v>7063756</v>
+        <v>7063742</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,32 +1730,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129407794</v>
+        <v>129407893</v>
       </c>
       <c r="B12" t="n">
-        <v>91517</v>
+        <v>79070</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560102</v>
+        <v>560059</v>
       </c>
       <c r="R12" t="n">
-        <v>7063742</v>
+        <v>7063756</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129407377</v>
+        <v>129410983</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>57730</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,34 +1848,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560226</v>
+        <v>559933</v>
       </c>
       <c r="R13" t="n">
-        <v>7063565</v>
+        <v>7063772</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,19 +1905,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>16:08</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>16:08</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1932,22 +1927,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129407592</v>
+        <v>129407377</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560233</v>
+        <v>560226</v>
       </c>
       <c r="R14" t="n">
-        <v>7063609</v>
+        <v>7063565</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2014,7 +2009,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2024,7 +2019,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129410983</v>
+        <v>129407592</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2062,34 +2057,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559933</v>
+        <v>560233</v>
       </c>
       <c r="R15" t="n">
-        <v>7063772</v>
+        <v>7063609</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2119,14 +2114,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2141,12 +2141,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2156,7 +2156,7 @@
         <v>129407859</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>129407762</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>129407351</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>129406811</v>
       </c>
       <c r="B19" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>129407821</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2703,49 +2703,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129407633</v>
+        <v>129410980</v>
       </c>
       <c r="B21" t="n">
-        <v>98727</v>
+        <v>57730</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560193</v>
+        <v>559994</v>
       </c>
       <c r="R21" t="n">
-        <v>7063641</v>
+        <v>7063702</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2775,19 +2771,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>16:20</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2802,22 +2793,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129410997</v>
+        <v>129407633</v>
       </c>
       <c r="B22" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2844,19 +2835,19 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559930</v>
+        <v>560193</v>
       </c>
       <c r="R22" t="n">
-        <v>7063777</v>
+        <v>7063641</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2886,75 +2877,88 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129410980</v>
+        <v>129410997</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>98756</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559994</v>
+        <v>559930</v>
       </c>
       <c r="R23" t="n">
-        <v>7063702</v>
+        <v>7063777</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2989,17 +2993,13 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3018,10 +3018,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129406681</v>
+        <v>129406824</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>80175</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,39 +3029,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560028</v>
+        <v>560095</v>
       </c>
       <c r="R24" t="n">
-        <v>7063663</v>
+        <v>7063636</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3093,7 +3088,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3103,12 +3098,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3135,10 +3125,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129406824</v>
+        <v>129406722</v>
       </c>
       <c r="B25" t="n">
-        <v>80149</v>
+        <v>79070</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3146,34 +3136,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560095</v>
+        <v>560046</v>
       </c>
       <c r="R25" t="n">
-        <v>7063636</v>
+        <v>7063665</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3205,7 +3195,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3215,7 +3205,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3242,10 +3232,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129406722</v>
+        <v>129406681</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>57730</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3253,34 +3243,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560046</v>
+        <v>560028</v>
       </c>
       <c r="R26" t="n">
-        <v>7063665</v>
+        <v>7063663</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3312,7 +3307,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3322,7 +3317,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3352,7 +3352,7 @@
         <v>129410981</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>129407124</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>129406968</v>
       </c>
       <c r="B29" t="n">
-        <v>80178</v>
+        <v>80204</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>129559957</v>
       </c>
       <c r="B30" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>129559998</v>
       </c>
       <c r="B31" t="n">
-        <v>88952</v>
+        <v>88980</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>129561392</v>
       </c>
       <c r="B32" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>129561840</v>
       </c>
       <c r="B33" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>129561826</v>
       </c>
       <c r="B34" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>129561598</v>
       </c>
       <c r="B35" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>129561747</v>
       </c>
       <c r="B36" t="n">
-        <v>83012</v>
+        <v>83039</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4343,10 +4343,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129561089</v>
+        <v>129561632</v>
       </c>
       <c r="B37" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4378,10 +4378,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560043</v>
+        <v>560075</v>
       </c>
       <c r="R37" t="n">
-        <v>7063692</v>
+        <v>7063677</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4440,10 +4440,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129561632</v>
+        <v>129561089</v>
       </c>
       <c r="B38" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560075</v>
+        <v>560043</v>
       </c>
       <c r="R38" t="n">
-        <v>7063677</v>
+        <v>7063692</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4540,7 +4540,7 @@
         <v>129561809</v>
       </c>
       <c r="B39" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>129559867</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>129561092</v>
       </c>
       <c r="B41" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>129562162</v>
       </c>
       <c r="B42" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>129562154</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 32793-2025 artfynd.xlsx
+++ b/artfynd/A 32793-2025 artfynd.xlsx
@@ -1837,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129410983</v>
+        <v>129407377</v>
       </c>
       <c r="B13" t="n">
-        <v>57730</v>
+        <v>79070</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,34 +1848,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559933</v>
+        <v>560226</v>
       </c>
       <c r="R13" t="n">
-        <v>7063772</v>
+        <v>7063565</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,14 +1905,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1927,19 +1932,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129407377</v>
+        <v>129407592</v>
       </c>
       <c r="B14" t="n">
         <v>79070</v>
@@ -1974,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560226</v>
+        <v>560233</v>
       </c>
       <c r="R14" t="n">
-        <v>7063565</v>
+        <v>7063609</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2009,7 +2014,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2019,7 +2024,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129407592</v>
+        <v>129410983</v>
       </c>
       <c r="B15" t="n">
-        <v>79070</v>
+        <v>57730</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2057,34 +2062,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560233</v>
+        <v>559933</v>
       </c>
       <c r="R15" t="n">
-        <v>7063609</v>
+        <v>7063772</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2114,19 +2119,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>16:17</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2141,12 +2141,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -3125,10 +3125,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129406722</v>
+        <v>129406681</v>
       </c>
       <c r="B25" t="n">
-        <v>79070</v>
+        <v>57730</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,34 +3136,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560046</v>
+        <v>560028</v>
       </c>
       <c r="R25" t="n">
-        <v>7063665</v>
+        <v>7063663</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3195,7 +3200,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3205,7 +3210,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3232,10 +3242,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129406681</v>
+        <v>129406722</v>
       </c>
       <c r="B26" t="n">
-        <v>57730</v>
+        <v>79070</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3243,39 +3253,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560028</v>
+        <v>560046</v>
       </c>
       <c r="R26" t="n">
-        <v>7063663</v>
+        <v>7063665</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3307,7 +3312,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3317,12 +3322,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 32793-2025 artfynd.xlsx
+++ b/artfynd/A 32793-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129395994</v>
       </c>
       <c r="B2" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129406836</v>
       </c>
       <c r="B3" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129411008</v>
+        <v>129406905</v>
       </c>
       <c r="B4" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,14 +920,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559922</v>
+        <v>560134</v>
       </c>
       <c r="R4" t="n">
-        <v>7063790</v>
+        <v>7063629</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,9 +957,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,12 +984,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -989,7 +999,7 @@
         <v>129406877</v>
       </c>
       <c r="B5" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129406905</v>
+        <v>129411008</v>
       </c>
       <c r="B6" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,14 +1134,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560134</v>
+        <v>559922</v>
       </c>
       <c r="R6" t="n">
-        <v>7063629</v>
+        <v>7063790</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,19 +1171,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,12 +1188,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1203,7 +1203,7 @@
         <v>129410982</v>
       </c>
       <c r="B7" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>129406697</v>
       </c>
       <c r="B8" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>129408046</v>
       </c>
       <c r="B9" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>129411007</v>
       </c>
       <c r="B10" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1623,32 +1623,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129407794</v>
+        <v>129407893</v>
       </c>
       <c r="B11" t="n">
-        <v>91545</v>
+        <v>79075</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>560102</v>
+        <v>560059</v>
       </c>
       <c r="R11" t="n">
-        <v>7063742</v>
+        <v>7063756</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,32 +1730,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129407893</v>
+        <v>129407794</v>
       </c>
       <c r="B12" t="n">
-        <v>79070</v>
+        <v>91551</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560059</v>
+        <v>560102</v>
       </c>
       <c r="R12" t="n">
-        <v>7063756</v>
+        <v>7063742</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1840,7 +1840,7 @@
         <v>129407377</v>
       </c>
       <c r="B13" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>129407592</v>
       </c>
       <c r="B14" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>129410983</v>
       </c>
       <c r="B15" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>129407859</v>
       </c>
       <c r="B16" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>129407762</v>
       </c>
       <c r="B17" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2367,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129407351</v>
+        <v>129406811</v>
       </c>
       <c r="B18" t="n">
-        <v>57730</v>
+        <v>57732</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2378,16 +2378,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2403,14 +2403,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560249</v>
+        <v>560083</v>
       </c>
       <c r="R18" t="n">
-        <v>7063529</v>
+        <v>7063653</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2452,12 +2452,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129406811</v>
+        <v>129407351</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2495,16 +2490,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2520,14 +2515,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560083</v>
+        <v>560249</v>
       </c>
       <c r="R19" t="n">
-        <v>7063653</v>
+        <v>7063529</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2559,7 +2554,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2569,7 +2564,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2599,7 +2599,7 @@
         <v>129407821</v>
       </c>
       <c r="B20" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2703,45 +2703,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129410980</v>
+        <v>129410997</v>
       </c>
       <c r="B21" t="n">
-        <v>57730</v>
+        <v>98768</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559994</v>
+        <v>559930</v>
       </c>
       <c r="R21" t="n">
-        <v>7063702</v>
+        <v>7063777</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2776,17 +2780,13 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2808,7 +2808,7 @@
         <v>129407633</v>
       </c>
       <c r="B22" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2916,49 +2916,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129410997</v>
+        <v>129410980</v>
       </c>
       <c r="B23" t="n">
-        <v>98756</v>
+        <v>57735</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559930</v>
+        <v>559994</v>
       </c>
       <c r="R23" t="n">
-        <v>7063777</v>
+        <v>7063702</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2993,13 +2989,17 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3021,7 +3021,7 @@
         <v>129406824</v>
       </c>
       <c r="B24" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>129406681</v>
       </c>
       <c r="B25" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>129406722</v>
       </c>
       <c r="B26" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>129410981</v>
       </c>
       <c r="B27" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>129407124</v>
       </c>
       <c r="B28" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>129406968</v>
       </c>
       <c r="B29" t="n">
-        <v>80204</v>
+        <v>80209</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>129559957</v>
       </c>
       <c r="B30" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>129559998</v>
       </c>
       <c r="B31" t="n">
-        <v>88980</v>
+        <v>88986</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3858,10 +3858,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129561392</v>
+        <v>129561826</v>
       </c>
       <c r="B32" t="n">
-        <v>91879</v>
+        <v>91587</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3869,21 +3869,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560043</v>
+        <v>560071</v>
       </c>
       <c r="R32" t="n">
-        <v>7063681</v>
+        <v>7063709</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3955,10 +3955,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129561840</v>
+        <v>129561598</v>
       </c>
       <c r="B33" t="n">
-        <v>91879</v>
+        <v>91587</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3966,21 +3966,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3990,10 +3990,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560074</v>
+        <v>560048</v>
       </c>
       <c r="R33" t="n">
-        <v>7063724</v>
+        <v>7063683</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4052,10 +4052,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129561826</v>
+        <v>129561840</v>
       </c>
       <c r="B34" t="n">
-        <v>91581</v>
+        <v>91885</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4063,21 +4063,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4087,10 +4087,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560071</v>
+        <v>560074</v>
       </c>
       <c r="R34" t="n">
-        <v>7063709</v>
+        <v>7063724</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4149,10 +4149,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129561598</v>
+        <v>129561392</v>
       </c>
       <c r="B35" t="n">
-        <v>91581</v>
+        <v>91885</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4160,21 +4160,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560048</v>
+        <v>560043</v>
       </c>
       <c r="R35" t="n">
-        <v>7063683</v>
+        <v>7063681</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4249,7 +4249,7 @@
         <v>129561747</v>
       </c>
       <c r="B36" t="n">
-        <v>83039</v>
+        <v>83044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4343,10 +4343,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129561632</v>
+        <v>129561089</v>
       </c>
       <c r="B37" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4378,10 +4378,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560075</v>
+        <v>560043</v>
       </c>
       <c r="R37" t="n">
-        <v>7063677</v>
+        <v>7063692</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4440,10 +4440,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129561089</v>
+        <v>129561632</v>
       </c>
       <c r="B38" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560043</v>
+        <v>560075</v>
       </c>
       <c r="R38" t="n">
-        <v>7063692</v>
+        <v>7063677</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4540,7 +4540,7 @@
         <v>129561809</v>
       </c>
       <c r="B39" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>129559867</v>
       </c>
       <c r="B40" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>129561092</v>
       </c>
       <c r="B41" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>129562162</v>
       </c>
       <c r="B42" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>129562154</v>
       </c>
       <c r="B43" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 32793-2025 artfynd.xlsx
+++ b/artfynd/A 32793-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129395994</v>
       </c>
       <c r="B2" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129406836</v>
       </c>
       <c r="B3" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129406905</v>
       </c>
       <c r="B4" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129406877</v>
+        <v>129411008</v>
       </c>
       <c r="B5" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,14 +1027,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560134</v>
+        <v>559922</v>
       </c>
       <c r="R5" t="n">
-        <v>7063639</v>
+        <v>7063790</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,19 +1064,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,22 +1081,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129411008</v>
+        <v>129406877</v>
       </c>
       <c r="B6" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,14 +1124,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559922</v>
+        <v>560134</v>
       </c>
       <c r="R6" t="n">
-        <v>7063790</v>
+        <v>7063639</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1171,9 +1161,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,12 +1188,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1203,7 +1203,7 @@
         <v>129410982</v>
       </c>
       <c r="B7" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>129406697</v>
       </c>
       <c r="B8" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>129408046</v>
       </c>
       <c r="B9" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>129411007</v>
       </c>
       <c r="B10" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>129407893</v>
       </c>
       <c r="B11" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>129407794</v>
       </c>
       <c r="B12" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>129407377</v>
       </c>
       <c r="B13" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>129407592</v>
       </c>
       <c r="B14" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>129410983</v>
       </c>
       <c r="B15" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>129407859</v>
       </c>
       <c r="B16" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>129407762</v>
       </c>
       <c r="B17" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2367,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129406811</v>
+        <v>129407351</v>
       </c>
       <c r="B18" t="n">
-        <v>57732</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2378,16 +2378,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2403,14 +2403,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560083</v>
+        <v>560249</v>
       </c>
       <c r="R18" t="n">
-        <v>7063653</v>
+        <v>7063529</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2452,7 +2452,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129407351</v>
+        <v>129406811</v>
       </c>
       <c r="B19" t="n">
-        <v>57735</v>
+        <v>57733</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2490,16 +2495,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2515,14 +2520,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560249</v>
+        <v>560083</v>
       </c>
       <c r="R19" t="n">
-        <v>7063529</v>
+        <v>7063653</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2554,7 +2559,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2564,12 +2569,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2599,7 +2599,7 @@
         <v>129407821</v>
       </c>
       <c r="B20" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>129410997</v>
       </c>
       <c r="B21" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>129407633</v>
       </c>
       <c r="B22" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>129410980</v>
       </c>
       <c r="B23" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3018,10 +3018,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129406824</v>
+        <v>129406722</v>
       </c>
       <c r="B24" t="n">
-        <v>80180</v>
+        <v>79076</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,34 +3029,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560095</v>
+        <v>560046</v>
       </c>
       <c r="R24" t="n">
-        <v>7063636</v>
+        <v>7063665</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3125,10 +3125,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129406681</v>
+        <v>129406824</v>
       </c>
       <c r="B25" t="n">
-        <v>57735</v>
+        <v>80181</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,39 +3136,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560028</v>
+        <v>560095</v>
       </c>
       <c r="R25" t="n">
-        <v>7063663</v>
+        <v>7063636</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3200,7 +3195,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3210,12 +3205,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3242,10 +3232,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129406722</v>
+        <v>129406681</v>
       </c>
       <c r="B26" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3253,34 +3243,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560046</v>
+        <v>560028</v>
       </c>
       <c r="R26" t="n">
-        <v>7063665</v>
+        <v>7063663</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3312,7 +3307,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3322,7 +3317,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3352,7 +3352,7 @@
         <v>129410981</v>
       </c>
       <c r="B27" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>129407124</v>
       </c>
       <c r="B28" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>129406968</v>
       </c>
       <c r="B29" t="n">
-        <v>80209</v>
+        <v>80210</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>129559957</v>
       </c>
       <c r="B30" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>129559998</v>
       </c>
       <c r="B31" t="n">
-        <v>88986</v>
+        <v>88987</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3858,10 +3858,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129561826</v>
+        <v>129561840</v>
       </c>
       <c r="B32" t="n">
-        <v>91587</v>
+        <v>91886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3869,21 +3869,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560071</v>
+        <v>560074</v>
       </c>
       <c r="R32" t="n">
-        <v>7063709</v>
+        <v>7063724</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3955,10 +3955,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129561598</v>
+        <v>129561826</v>
       </c>
       <c r="B33" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3990,10 +3990,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560048</v>
+        <v>560071</v>
       </c>
       <c r="R33" t="n">
-        <v>7063683</v>
+        <v>7063709</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4052,10 +4052,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129561840</v>
+        <v>129561392</v>
       </c>
       <c r="B34" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4087,10 +4087,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560074</v>
+        <v>560043</v>
       </c>
       <c r="R34" t="n">
-        <v>7063724</v>
+        <v>7063681</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4149,10 +4149,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129561392</v>
+        <v>129561598</v>
       </c>
       <c r="B35" t="n">
-        <v>91885</v>
+        <v>91588</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4160,21 +4160,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560043</v>
+        <v>560048</v>
       </c>
       <c r="R35" t="n">
-        <v>7063681</v>
+        <v>7063683</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4249,7 +4249,7 @@
         <v>129561747</v>
       </c>
       <c r="B36" t="n">
-        <v>83044</v>
+        <v>83045</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>129561089</v>
       </c>
       <c r="B37" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>129561632</v>
       </c>
       <c r="B38" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>129561809</v>
       </c>
       <c r="B39" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>129559867</v>
       </c>
       <c r="B40" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>129561092</v>
       </c>
       <c r="B41" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>129562162</v>
       </c>
       <c r="B42" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>129562154</v>
       </c>
       <c r="B43" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 32793-2025 artfynd.xlsx
+++ b/artfynd/A 32793-2025 artfynd.xlsx
@@ -2703,49 +2703,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129410997</v>
+        <v>129410980</v>
       </c>
       <c r="B21" t="n">
-        <v>98769</v>
+        <v>57736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559930</v>
+        <v>559994</v>
       </c>
       <c r="R21" t="n">
-        <v>7063777</v>
+        <v>7063702</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2780,13 +2776,17 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2805,7 +2805,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129407633</v>
+        <v>129410997</v>
       </c>
       <c r="B22" t="n">
         <v>98769</v>
@@ -2835,19 +2835,19 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560193</v>
+        <v>559930</v>
       </c>
       <c r="R22" t="n">
-        <v>7063641</v>
+        <v>7063777</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,84 +2877,79 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129410980</v>
+        <v>129407633</v>
       </c>
       <c r="B23" t="n">
-        <v>57736</v>
+        <v>98769</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559994</v>
+        <v>560193</v>
       </c>
       <c r="R23" t="n">
-        <v>7063702</v>
+        <v>7063641</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2984,14 +2979,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3006,22 +3006,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129406722</v>
+        <v>129406681</v>
       </c>
       <c r="B24" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,34 +3029,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560046</v>
+        <v>560028</v>
       </c>
       <c r="R24" t="n">
-        <v>7063665</v>
+        <v>7063663</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3088,7 +3093,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3098,7 +3103,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3125,10 +3135,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129406824</v>
+        <v>129406722</v>
       </c>
       <c r="B25" t="n">
-        <v>80181</v>
+        <v>79076</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,34 +3146,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560095</v>
+        <v>560046</v>
       </c>
       <c r="R25" t="n">
-        <v>7063636</v>
+        <v>7063665</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3195,7 +3205,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3205,7 +3215,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3232,10 +3242,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129406681</v>
+        <v>129406824</v>
       </c>
       <c r="B26" t="n">
-        <v>57736</v>
+        <v>80181</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3243,39 +3253,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560028</v>
+        <v>560095</v>
       </c>
       <c r="R26" t="n">
-        <v>7063663</v>
+        <v>7063636</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3307,7 +3312,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3317,12 +3322,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3858,10 +3858,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129561840</v>
+        <v>129561826</v>
       </c>
       <c r="B32" t="n">
-        <v>91886</v>
+        <v>91588</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3869,21 +3869,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560074</v>
+        <v>560071</v>
       </c>
       <c r="R32" t="n">
-        <v>7063724</v>
+        <v>7063709</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3955,10 +3955,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129561826</v>
+        <v>129561840</v>
       </c>
       <c r="B33" t="n">
-        <v>91588</v>
+        <v>91886</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3966,21 +3966,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3990,10 +3990,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560071</v>
+        <v>560074</v>
       </c>
       <c r="R33" t="n">
-        <v>7063709</v>
+        <v>7063724</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4052,10 +4052,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129561392</v>
+        <v>129561598</v>
       </c>
       <c r="B34" t="n">
-        <v>91886</v>
+        <v>91588</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4063,21 +4063,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4087,10 +4087,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560043</v>
+        <v>560048</v>
       </c>
       <c r="R34" t="n">
-        <v>7063681</v>
+        <v>7063683</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4149,10 +4149,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129561598</v>
+        <v>129561392</v>
       </c>
       <c r="B35" t="n">
-        <v>91588</v>
+        <v>91886</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4160,21 +4160,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560048</v>
+        <v>560043</v>
       </c>
       <c r="R35" t="n">
-        <v>7063683</v>
+        <v>7063681</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>

--- a/artfynd/A 32793-2025 artfynd.xlsx
+++ b/artfynd/A 32793-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129395994</v>
       </c>
       <c r="B2" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129406836</v>
       </c>
       <c r="B3" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129406905</v>
+        <v>129406697</v>
       </c>
       <c r="B4" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +900,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560134</v>
+        <v>560040</v>
       </c>
       <c r="R4" t="n">
-        <v>7063629</v>
+        <v>7063656</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +974,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129411008</v>
+        <v>129406905</v>
       </c>
       <c r="B5" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,14 +1037,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559922</v>
+        <v>560134</v>
       </c>
       <c r="R5" t="n">
-        <v>7063790</v>
+        <v>7063629</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,9 +1074,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,22 +1101,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129406877</v>
+        <v>129411008</v>
       </c>
       <c r="B6" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,14 +1144,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560134</v>
+        <v>559922</v>
       </c>
       <c r="R6" t="n">
-        <v>7063639</v>
+        <v>7063790</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,19 +1181,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,22 +1198,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129410982</v>
+        <v>129406877</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,34 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559966</v>
+        <v>560134</v>
       </c>
       <c r="R7" t="n">
-        <v>7063789</v>
+        <v>7063639</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1268,14 +1278,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1290,19 +1305,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129406697</v>
+        <v>129410982</v>
       </c>
       <c r="B8" t="n">
         <v>57736</v>
@@ -1331,21 +1346,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560040</v>
+        <v>559966</v>
       </c>
       <c r="R8" t="n">
-        <v>7063656</v>
+        <v>7063789</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1375,24 +1385,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1407,12 +1407,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1422,7 +1422,7 @@
         <v>129408046</v>
       </c>
       <c r="B9" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>129411007</v>
       </c>
       <c r="B10" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>129407893</v>
       </c>
       <c r="B11" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>129407794</v>
       </c>
       <c r="B12" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>129407377</v>
       </c>
       <c r="B13" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>129407592</v>
       </c>
       <c r="B14" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>129407859</v>
       </c>
       <c r="B16" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>129407762</v>
       </c>
       <c r="B17" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2367,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129407351</v>
+        <v>129406811</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2378,16 +2378,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2403,14 +2403,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560249</v>
+        <v>560083</v>
       </c>
       <c r="R18" t="n">
-        <v>7063529</v>
+        <v>7063653</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2452,12 +2452,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129406811</v>
+        <v>129407351</v>
       </c>
       <c r="B19" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2495,16 +2490,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2520,14 +2515,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560083</v>
+        <v>560249</v>
       </c>
       <c r="R19" t="n">
-        <v>7063653</v>
+        <v>7063529</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2559,7 +2554,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2569,7 +2564,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2599,7 +2599,7 @@
         <v>129407821</v>
       </c>
       <c r="B20" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>129410997</v>
       </c>
       <c r="B22" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>129407633</v>
       </c>
       <c r="B23" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3018,10 +3018,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129406681</v>
+        <v>129406824</v>
       </c>
       <c r="B24" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,39 +3029,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560028</v>
+        <v>560095</v>
       </c>
       <c r="R24" t="n">
-        <v>7063663</v>
+        <v>7063636</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3093,7 +3088,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3103,12 +3098,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3138,7 +3128,7 @@
         <v>129406722</v>
       </c>
       <c r="B25" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3242,10 +3232,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129406824</v>
+        <v>129406681</v>
       </c>
       <c r="B26" t="n">
-        <v>80181</v>
+        <v>57736</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3253,34 +3243,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560095</v>
+        <v>560028</v>
       </c>
       <c r="R26" t="n">
-        <v>7063636</v>
+        <v>7063663</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3312,7 +3307,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3322,7 +3317,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3453,7 +3453,7 @@
         <v>129407124</v>
       </c>
       <c r="B28" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>129406968</v>
       </c>
       <c r="B29" t="n">
-        <v>80210</v>
+        <v>80215</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>129559957</v>
       </c>
       <c r="B30" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>129559998</v>
       </c>
       <c r="B31" t="n">
-        <v>88987</v>
+        <v>88992</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3858,10 +3858,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129561826</v>
+        <v>129561598</v>
       </c>
       <c r="B32" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560071</v>
+        <v>560048</v>
       </c>
       <c r="R32" t="n">
-        <v>7063709</v>
+        <v>7063683</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3955,10 +3955,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129561840</v>
+        <v>129561826</v>
       </c>
       <c r="B33" t="n">
-        <v>91886</v>
+        <v>91593</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3966,21 +3966,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3990,10 +3990,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560074</v>
+        <v>560071</v>
       </c>
       <c r="R33" t="n">
-        <v>7063724</v>
+        <v>7063709</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4052,10 +4052,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129561598</v>
+        <v>129561392</v>
       </c>
       <c r="B34" t="n">
-        <v>91588</v>
+        <v>91891</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4063,21 +4063,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4087,10 +4087,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560048</v>
+        <v>560043</v>
       </c>
       <c r="R34" t="n">
-        <v>7063683</v>
+        <v>7063681</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4149,10 +4149,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129561392</v>
+        <v>129561840</v>
       </c>
       <c r="B35" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560043</v>
+        <v>560074</v>
       </c>
       <c r="R35" t="n">
-        <v>7063681</v>
+        <v>7063724</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4249,7 +4249,7 @@
         <v>129561747</v>
       </c>
       <c r="B36" t="n">
-        <v>83045</v>
+        <v>83050</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>129561089</v>
       </c>
       <c r="B37" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>129561632</v>
       </c>
       <c r="B38" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>129561809</v>
       </c>
       <c r="B39" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>129561092</v>
       </c>
       <c r="B41" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 32793-2025 artfynd.xlsx
+++ b/artfynd/A 32793-2025 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129406697</v>
+        <v>129406905</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,39 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560040</v>
+        <v>560134</v>
       </c>
       <c r="R4" t="n">
-        <v>7063656</v>
+        <v>7063629</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:39</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129406905</v>
+        <v>129406877</v>
       </c>
       <c r="B5" t="n">
         <v>79081</v>
@@ -1044,7 +1034,7 @@
         <v>560134</v>
       </c>
       <c r="R5" t="n">
-        <v>7063629</v>
+        <v>7063639</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129411008</v>
+        <v>129410982</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559922</v>
+        <v>559966</v>
       </c>
       <c r="R6" t="n">
-        <v>7063790</v>
+        <v>7063789</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,6 +1174,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129406877</v>
+        <v>129406697</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,34 +1216,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560134</v>
+        <v>560040</v>
       </c>
       <c r="R7" t="n">
-        <v>7063639</v>
+        <v>7063656</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129410982</v>
+        <v>129411008</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559966</v>
+        <v>559922</v>
       </c>
       <c r="R8" t="n">
-        <v>7063789</v>
+        <v>7063790</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,11 +1393,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1623,32 +1623,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129407893</v>
+        <v>129407794</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>91557</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>560059</v>
+        <v>560102</v>
       </c>
       <c r="R11" t="n">
-        <v>7063756</v>
+        <v>7063742</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,32 +1730,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129407794</v>
+        <v>129407893</v>
       </c>
       <c r="B12" t="n">
-        <v>91557</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560102</v>
+        <v>560059</v>
       </c>
       <c r="R12" t="n">
-        <v>7063742</v>
+        <v>7063756</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129407377</v>
+        <v>129410983</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,34 +1848,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560226</v>
+        <v>559933</v>
       </c>
       <c r="R13" t="n">
-        <v>7063565</v>
+        <v>7063772</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,19 +1905,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>16:08</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>16:08</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1932,19 +1927,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129407592</v>
+        <v>129407377</v>
       </c>
       <c r="B14" t="n">
         <v>79081</v>
@@ -1979,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560233</v>
+        <v>560226</v>
       </c>
       <c r="R14" t="n">
-        <v>7063609</v>
+        <v>7063565</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2014,7 +2009,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2024,7 +2019,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129410983</v>
+        <v>129407592</v>
       </c>
       <c r="B15" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2062,34 +2057,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559933</v>
+        <v>560233</v>
       </c>
       <c r="R15" t="n">
-        <v>7063772</v>
+        <v>7063609</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2119,14 +2114,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2141,12 +2141,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2805,7 +2805,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129410997</v>
+        <v>129407633</v>
       </c>
       <c r="B22" t="n">
         <v>98774</v>
@@ -2835,19 +2835,19 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559930</v>
+        <v>560193</v>
       </c>
       <c r="R22" t="n">
-        <v>7063777</v>
+        <v>7063641</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,37 +2877,46 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129407633</v>
+        <v>129410997</v>
       </c>
       <c r="B23" t="n">
         <v>98774</v>
@@ -2937,19 +2946,19 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560193</v>
+        <v>559930</v>
       </c>
       <c r="R23" t="n">
-        <v>7063641</v>
+        <v>7063777</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2979,39 +2988,30 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3125,10 +3125,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129406722</v>
+        <v>129406681</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,34 +3136,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560046</v>
+        <v>560028</v>
       </c>
       <c r="R25" t="n">
-        <v>7063665</v>
+        <v>7063663</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3195,7 +3200,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3205,7 +3210,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3232,10 +3242,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129406681</v>
+        <v>129406722</v>
       </c>
       <c r="B26" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3243,39 +3253,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560028</v>
+        <v>560046</v>
       </c>
       <c r="R26" t="n">
-        <v>7063663</v>
+        <v>7063665</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3307,7 +3312,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3317,12 +3322,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3858,10 +3858,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129561598</v>
+        <v>129561392</v>
       </c>
       <c r="B32" t="n">
-        <v>91593</v>
+        <v>91891</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3869,21 +3869,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560048</v>
+        <v>560043</v>
       </c>
       <c r="R32" t="n">
-        <v>7063683</v>
+        <v>7063681</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3955,10 +3955,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129561826</v>
+        <v>129561840</v>
       </c>
       <c r="B33" t="n">
-        <v>91593</v>
+        <v>91891</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3966,21 +3966,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3990,10 +3990,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560071</v>
+        <v>560074</v>
       </c>
       <c r="R33" t="n">
-        <v>7063709</v>
+        <v>7063724</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4052,10 +4052,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129561392</v>
+        <v>129561826</v>
       </c>
       <c r="B34" t="n">
-        <v>91891</v>
+        <v>91593</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4063,21 +4063,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4087,10 +4087,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560043</v>
+        <v>560071</v>
       </c>
       <c r="R34" t="n">
-        <v>7063681</v>
+        <v>7063709</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4149,10 +4149,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129561840</v>
+        <v>129561598</v>
       </c>
       <c r="B35" t="n">
-        <v>91891</v>
+        <v>91593</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4160,21 +4160,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560074</v>
+        <v>560048</v>
       </c>
       <c r="R35" t="n">
-        <v>7063724</v>
+        <v>7063683</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>

--- a/artfynd/A 32793-2025 artfynd.xlsx
+++ b/artfynd/A 32793-2025 artfynd.xlsx
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129406905</v>
+        <v>129411008</v>
       </c>
       <c r="B4" t="n">
         <v>79081</v>
@@ -920,14 +920,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560134</v>
+        <v>559922</v>
       </c>
       <c r="R4" t="n">
-        <v>7063629</v>
+        <v>7063790</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,19 +957,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,19 +974,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129406877</v>
+        <v>129406905</v>
       </c>
       <c r="B5" t="n">
         <v>79081</v>
@@ -1034,7 +1024,7 @@
         <v>560134</v>
       </c>
       <c r="R5" t="n">
-        <v>7063639</v>
+        <v>7063629</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129410982</v>
+        <v>129406877</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,34 +1104,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559966</v>
+        <v>560134</v>
       </c>
       <c r="R6" t="n">
-        <v>7063789</v>
+        <v>7063639</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1171,14 +1161,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,19 +1188,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129406697</v>
+        <v>129410982</v>
       </c>
       <c r="B7" t="n">
         <v>57736</v>
@@ -1234,21 +1229,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560040</v>
+        <v>559966</v>
       </c>
       <c r="R7" t="n">
-        <v>7063656</v>
+        <v>7063789</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1278,24 +1268,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,22 +1290,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129411008</v>
+        <v>129406697</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,34 +1313,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559922</v>
+        <v>560040</v>
       </c>
       <c r="R8" t="n">
-        <v>7063790</v>
+        <v>7063656</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,9 +1375,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1407,12 +1407,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129410983</v>
+        <v>129407377</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,34 +1848,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559933</v>
+        <v>560226</v>
       </c>
       <c r="R13" t="n">
-        <v>7063772</v>
+        <v>7063565</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,14 +1905,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1927,19 +1932,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129407377</v>
+        <v>129407592</v>
       </c>
       <c r="B14" t="n">
         <v>79081</v>
@@ -1974,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560226</v>
+        <v>560233</v>
       </c>
       <c r="R14" t="n">
-        <v>7063565</v>
+        <v>7063609</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2009,7 +2014,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2019,7 +2024,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129407592</v>
+        <v>129410983</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2057,34 +2062,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560233</v>
+        <v>559933</v>
       </c>
       <c r="R15" t="n">
-        <v>7063609</v>
+        <v>7063772</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2114,19 +2119,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>16:17</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2141,12 +2141,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2703,45 +2703,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129410980</v>
+        <v>129410997</v>
       </c>
       <c r="B21" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559994</v>
+        <v>559930</v>
       </c>
       <c r="R21" t="n">
-        <v>7063702</v>
+        <v>7063777</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2776,17 +2780,13 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2916,49 +2916,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129410997</v>
+        <v>129410980</v>
       </c>
       <c r="B23" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559930</v>
+        <v>559994</v>
       </c>
       <c r="R23" t="n">
-        <v>7063777</v>
+        <v>7063702</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2993,13 +2989,17 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3125,10 +3125,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129406681</v>
+        <v>129406722</v>
       </c>
       <c r="B25" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,39 +3136,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560028</v>
+        <v>560046</v>
       </c>
       <c r="R25" t="n">
-        <v>7063663</v>
+        <v>7063665</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3200,7 +3195,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3210,12 +3205,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3242,10 +3232,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129406722</v>
+        <v>129406681</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3253,34 +3243,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560046</v>
+        <v>560028</v>
       </c>
       <c r="R26" t="n">
-        <v>7063665</v>
+        <v>7063663</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3312,7 +3307,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3322,7 +3317,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 32793-2025 artfynd.xlsx
+++ b/artfynd/A 32793-2025 artfynd.xlsx
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129411008</v>
+        <v>129406905</v>
       </c>
       <c r="B4" t="n">
         <v>79081</v>
@@ -920,14 +920,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559922</v>
+        <v>560134</v>
       </c>
       <c r="R4" t="n">
-        <v>7063790</v>
+        <v>7063629</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,9 +957,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,19 +984,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129406905</v>
+        <v>129411008</v>
       </c>
       <c r="B5" t="n">
         <v>79081</v>
@@ -1017,14 +1027,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560134</v>
+        <v>559922</v>
       </c>
       <c r="R5" t="n">
-        <v>7063629</v>
+        <v>7063790</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,19 +1064,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,12 +1081,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1623,32 +1623,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129407794</v>
+        <v>129407893</v>
       </c>
       <c r="B11" t="n">
-        <v>91557</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>560102</v>
+        <v>560059</v>
       </c>
       <c r="R11" t="n">
-        <v>7063742</v>
+        <v>7063756</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,32 +1730,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129407893</v>
+        <v>129407794</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>91557</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560059</v>
+        <v>560102</v>
       </c>
       <c r="R12" t="n">
-        <v>7063756</v>
+        <v>7063742</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1944,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129407592</v>
+        <v>129410983</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1955,34 +1955,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560233</v>
+        <v>559933</v>
       </c>
       <c r="R14" t="n">
-        <v>7063609</v>
+        <v>7063772</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2012,19 +2012,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:17</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2039,22 +2034,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129410983</v>
+        <v>129407592</v>
       </c>
       <c r="B15" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2062,34 +2057,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559933</v>
+        <v>560233</v>
       </c>
       <c r="R15" t="n">
-        <v>7063772</v>
+        <v>7063609</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2119,14 +2114,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2141,12 +2141,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2703,49 +2703,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129410997</v>
+        <v>129410980</v>
       </c>
       <c r="B21" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559930</v>
+        <v>559994</v>
       </c>
       <c r="R21" t="n">
-        <v>7063777</v>
+        <v>7063702</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2780,13 +2776,17 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2805,7 +2805,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129407633</v>
+        <v>129410997</v>
       </c>
       <c r="B22" t="n">
         <v>98774</v>
@@ -2835,19 +2835,19 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560193</v>
+        <v>559930</v>
       </c>
       <c r="R22" t="n">
-        <v>7063641</v>
+        <v>7063777</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,84 +2877,79 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129410980</v>
+        <v>129407633</v>
       </c>
       <c r="B23" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559994</v>
+        <v>560193</v>
       </c>
       <c r="R23" t="n">
-        <v>7063702</v>
+        <v>7063641</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2984,14 +2979,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3006,12 +3006,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -4052,7 +4052,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129561826</v>
+        <v>129561598</v>
       </c>
       <c r="B34" t="n">
         <v>91593</v>
@@ -4087,10 +4087,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560071</v>
+        <v>560048</v>
       </c>
       <c r="R34" t="n">
-        <v>7063709</v>
+        <v>7063683</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4149,7 +4149,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129561598</v>
+        <v>129561826</v>
       </c>
       <c r="B35" t="n">
         <v>91593</v>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560048</v>
+        <v>560071</v>
       </c>
       <c r="R35" t="n">
-        <v>7063683</v>
+        <v>7063709</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129561089</v>
+        <v>129561632</v>
       </c>
       <c r="B37" t="n">
         <v>91593</v>
@@ -4378,10 +4378,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560043</v>
+        <v>560075</v>
       </c>
       <c r="R37" t="n">
-        <v>7063692</v>
+        <v>7063677</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4440,7 +4440,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129561632</v>
+        <v>129561089</v>
       </c>
       <c r="B38" t="n">
         <v>91593</v>
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560075</v>
+        <v>560043</v>
       </c>
       <c r="R38" t="n">
-        <v>7063677</v>
+        <v>7063692</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>

--- a/artfynd/A 32793-2025 artfynd.xlsx
+++ b/artfynd/A 32793-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129395994</v>
       </c>
       <c r="B2" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129406905</v>
+        <v>129410982</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560134</v>
+        <v>559966</v>
       </c>
       <c r="R4" t="n">
-        <v>7063629</v>
+        <v>7063789</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,19 +957,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:49</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,22 +979,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129411008</v>
+        <v>129406697</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +1002,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559922</v>
+        <v>560040</v>
       </c>
       <c r="R5" t="n">
-        <v>7063790</v>
+        <v>7063656</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,9 +1064,24 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,19 +1096,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129406877</v>
+        <v>129411008</v>
       </c>
       <c r="B6" t="n">
         <v>79081</v>
@@ -1124,14 +1139,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560134</v>
+        <v>559922</v>
       </c>
       <c r="R6" t="n">
-        <v>7063639</v>
+        <v>7063790</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,19 +1176,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,22 +1193,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129410982</v>
+        <v>129406905</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,34 +1216,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559966</v>
+        <v>560134</v>
       </c>
       <c r="R7" t="n">
-        <v>7063789</v>
+        <v>7063629</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1268,14 +1273,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1290,22 +1300,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129406697</v>
+        <v>129406877</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1313,39 +1323,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560040</v>
+        <v>560134</v>
       </c>
       <c r="R8" t="n">
-        <v>7063656</v>
+        <v>7063639</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,7 +1382,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1387,12 +1392,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:39</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1733,7 +1733,7 @@
         <v>129407794</v>
       </c>
       <c r="B12" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129410983</v>
+        <v>129407592</v>
       </c>
       <c r="B14" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1955,34 +1955,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559933</v>
+        <v>560233</v>
       </c>
       <c r="R14" t="n">
-        <v>7063772</v>
+        <v>7063609</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2012,14 +2012,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2034,22 +2039,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129407592</v>
+        <v>129410983</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2057,34 +2062,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560233</v>
+        <v>559933</v>
       </c>
       <c r="R15" t="n">
-        <v>7063609</v>
+        <v>7063772</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2114,19 +2119,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>16:17</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2141,12 +2141,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2805,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129410997</v>
+        <v>129407633</v>
       </c>
       <c r="B22" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2835,19 +2835,19 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559930</v>
+        <v>560193</v>
       </c>
       <c r="R22" t="n">
-        <v>7063777</v>
+        <v>7063641</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,40 +2877,49 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129407633</v>
+        <v>129410997</v>
       </c>
       <c r="B23" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2937,19 +2946,19 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560193</v>
+        <v>559930</v>
       </c>
       <c r="R23" t="n">
-        <v>7063641</v>
+        <v>7063777</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2979,49 +2988,40 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129406824</v>
+        <v>129406722</v>
       </c>
       <c r="B24" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,34 +3029,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560095</v>
+        <v>560046</v>
       </c>
       <c r="R24" t="n">
-        <v>7063636</v>
+        <v>7063665</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3125,10 +3125,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129406722</v>
+        <v>129406824</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,34 +3136,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560046</v>
+        <v>560095</v>
       </c>
       <c r="R25" t="n">
-        <v>7063665</v>
+        <v>7063636</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3667,7 +3667,7 @@
         <v>129559957</v>
       </c>
       <c r="B30" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>129559998</v>
       </c>
       <c r="B31" t="n">
-        <v>88992</v>
+        <v>88996</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3858,10 +3858,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129561392</v>
+        <v>129561826</v>
       </c>
       <c r="B32" t="n">
-        <v>91891</v>
+        <v>91597</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3869,21 +3869,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560043</v>
+        <v>560071</v>
       </c>
       <c r="R32" t="n">
-        <v>7063681</v>
+        <v>7063709</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3955,10 +3955,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129561840</v>
+        <v>129561598</v>
       </c>
       <c r="B33" t="n">
-        <v>91891</v>
+        <v>91597</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3966,21 +3966,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3990,10 +3990,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560074</v>
+        <v>560048</v>
       </c>
       <c r="R33" t="n">
-        <v>7063724</v>
+        <v>7063683</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4052,10 +4052,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129561598</v>
+        <v>129561392</v>
       </c>
       <c r="B34" t="n">
-        <v>91593</v>
+        <v>91895</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4063,21 +4063,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4087,10 +4087,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560048</v>
+        <v>560043</v>
       </c>
       <c r="R34" t="n">
-        <v>7063683</v>
+        <v>7063681</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4149,10 +4149,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129561826</v>
+        <v>129561840</v>
       </c>
       <c r="B35" t="n">
-        <v>91593</v>
+        <v>91895</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4160,21 +4160,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560071</v>
+        <v>560074</v>
       </c>
       <c r="R35" t="n">
-        <v>7063709</v>
+        <v>7063724</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4343,10 +4343,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129561632</v>
+        <v>129561089</v>
       </c>
       <c r="B37" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4378,10 +4378,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560075</v>
+        <v>560043</v>
       </c>
       <c r="R37" t="n">
-        <v>7063677</v>
+        <v>7063692</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4440,10 +4440,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129561089</v>
+        <v>129561632</v>
       </c>
       <c r="B38" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560043</v>
+        <v>560075</v>
       </c>
       <c r="R38" t="n">
-        <v>7063692</v>
+        <v>7063677</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4540,7 +4540,7 @@
         <v>129561809</v>
       </c>
       <c r="B39" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>129561092</v>
       </c>
       <c r="B41" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 32793-2025 artfynd.xlsx
+++ b/artfynd/A 32793-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129395994</v>
       </c>
       <c r="B2" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129410982</v>
+        <v>129406905</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559966</v>
+        <v>560134</v>
       </c>
       <c r="R4" t="n">
-        <v>7063789</v>
+        <v>7063629</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,14 +957,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,12 +984,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1205,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129406905</v>
+        <v>129406877</v>
       </c>
       <c r="B7" t="n">
         <v>79081</v>
@@ -1243,7 +1248,7 @@
         <v>560134</v>
       </c>
       <c r="R7" t="n">
-        <v>7063629</v>
+        <v>7063639</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1285,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129406877</v>
+        <v>129410982</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,34 +1328,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560134</v>
+        <v>559966</v>
       </c>
       <c r="R8" t="n">
-        <v>7063639</v>
+        <v>7063789</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1380,19 +1385,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:48</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1407,19 +1407,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129408046</v>
+        <v>129411007</v>
       </c>
       <c r="B9" t="n">
         <v>79081</v>
@@ -1450,14 +1450,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560033</v>
+        <v>559954</v>
       </c>
       <c r="R9" t="n">
-        <v>7063815</v>
+        <v>7063768</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1487,19 +1487,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>16:42</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>16:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1514,19 +1504,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129411007</v>
+        <v>129408046</v>
       </c>
       <c r="B10" t="n">
         <v>79081</v>
@@ -1557,14 +1547,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559954</v>
+        <v>560033</v>
       </c>
       <c r="R10" t="n">
-        <v>7063768</v>
+        <v>7063815</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1594,9 +1584,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1611,12 +1611,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1733,7 +1733,7 @@
         <v>129407794</v>
       </c>
       <c r="B12" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1837,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129407377</v>
+        <v>129410983</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,34 +1848,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560226</v>
+        <v>559933</v>
       </c>
       <c r="R13" t="n">
-        <v>7063565</v>
+        <v>7063772</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,19 +1905,14 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>16:08</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>16:08</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1932,19 +1927,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129407592</v>
+        <v>129407377</v>
       </c>
       <c r="B14" t="n">
         <v>79081</v>
@@ -1979,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560233</v>
+        <v>560226</v>
       </c>
       <c r="R14" t="n">
-        <v>7063609</v>
+        <v>7063565</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2014,7 +2009,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2024,7 +2019,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129410983</v>
+        <v>129407592</v>
       </c>
       <c r="B15" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2062,34 +2057,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559933</v>
+        <v>560233</v>
       </c>
       <c r="R15" t="n">
-        <v>7063772</v>
+        <v>7063609</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2119,14 +2114,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2141,12 +2141,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2367,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129406811</v>
+        <v>129407351</v>
       </c>
       <c r="B18" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2378,16 +2378,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2403,14 +2403,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560083</v>
+        <v>560249</v>
       </c>
       <c r="R18" t="n">
-        <v>7063653</v>
+        <v>7063529</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2452,7 +2452,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129407351</v>
+        <v>129406811</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2490,16 +2495,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2515,14 +2520,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560249</v>
+        <v>560083</v>
       </c>
       <c r="R19" t="n">
-        <v>7063529</v>
+        <v>7063653</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2554,7 +2559,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2564,12 +2569,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2805,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129407633</v>
+        <v>129410997</v>
       </c>
       <c r="B22" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2835,19 +2835,19 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Middagsmyran, Middagsmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560193</v>
+        <v>559930</v>
       </c>
       <c r="R22" t="n">
-        <v>7063641</v>
+        <v>7063777</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,49 +2877,40 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129410997</v>
+        <v>129407633</v>
       </c>
       <c r="B23" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2946,19 +2937,19 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Middagsmyran, Middagsmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559930</v>
+        <v>560193</v>
       </c>
       <c r="R23" t="n">
-        <v>7063777</v>
+        <v>7063641</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2988,30 +2979,39 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3667,7 +3667,7 @@
         <v>129559957</v>
       </c>
       <c r="B30" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>129559998</v>
       </c>
       <c r="B31" t="n">
-        <v>88996</v>
+        <v>88998</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3858,10 +3858,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129561826</v>
+        <v>129561392</v>
       </c>
       <c r="B32" t="n">
-        <v>91597</v>
+        <v>91897</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3869,21 +3869,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560071</v>
+        <v>560043</v>
       </c>
       <c r="R32" t="n">
-        <v>7063709</v>
+        <v>7063681</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3955,10 +3955,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129561598</v>
+        <v>129561840</v>
       </c>
       <c r="B33" t="n">
-        <v>91597</v>
+        <v>91897</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3966,21 +3966,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3990,10 +3990,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560048</v>
+        <v>560074</v>
       </c>
       <c r="R33" t="n">
-        <v>7063683</v>
+        <v>7063724</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4052,10 +4052,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129561392</v>
+        <v>129561826</v>
       </c>
       <c r="B34" t="n">
-        <v>91895</v>
+        <v>91599</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4063,21 +4063,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4087,10 +4087,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560043</v>
+        <v>560071</v>
       </c>
       <c r="R34" t="n">
-        <v>7063681</v>
+        <v>7063709</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4149,10 +4149,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129561840</v>
+        <v>129561598</v>
       </c>
       <c r="B35" t="n">
-        <v>91895</v>
+        <v>91599</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4160,21 +4160,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560074</v>
+        <v>560048</v>
       </c>
       <c r="R35" t="n">
-        <v>7063724</v>
+        <v>7063683</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4249,7 +4249,7 @@
         <v>129561747</v>
       </c>
       <c r="B36" t="n">
-        <v>83050</v>
+        <v>83052</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>129561089</v>
       </c>
       <c r="B37" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>129561632</v>
       </c>
       <c r="B38" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>129561809</v>
       </c>
       <c r="B39" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>129561092</v>
       </c>
       <c r="B41" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 32793-2025 artfynd.xlsx
+++ b/artfynd/A 32793-2025 artfynd.xlsx
@@ -3858,10 +3858,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129561392</v>
+        <v>129561598</v>
       </c>
       <c r="B32" t="n">
-        <v>91897</v>
+        <v>91599</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3869,21 +3869,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560043</v>
+        <v>560048</v>
       </c>
       <c r="R32" t="n">
-        <v>7063681</v>
+        <v>7063683</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3955,7 +3955,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129561840</v>
+        <v>129561392</v>
       </c>
       <c r="B33" t="n">
         <v>91897</v>
@@ -3990,10 +3990,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560074</v>
+        <v>560043</v>
       </c>
       <c r="R33" t="n">
-        <v>7063724</v>
+        <v>7063681</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4052,10 +4052,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129561826</v>
+        <v>129561840</v>
       </c>
       <c r="B34" t="n">
-        <v>91599</v>
+        <v>91897</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4063,21 +4063,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4087,10 +4087,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560071</v>
+        <v>560074</v>
       </c>
       <c r="R34" t="n">
-        <v>7063709</v>
+        <v>7063724</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4149,7 +4149,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129561598</v>
+        <v>129561826</v>
       </c>
       <c r="B35" t="n">
         <v>91599</v>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560048</v>
+        <v>560071</v>
       </c>
       <c r="R35" t="n">
-        <v>7063683</v>
+        <v>7063709</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>

--- a/artfynd/A 32793-2025 artfynd.xlsx
+++ b/artfynd/A 32793-2025 artfynd.xlsx
@@ -3667,7 +3667,7 @@
         <v>129559957</v>
       </c>
       <c r="B30" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>129559998</v>
       </c>
       <c r="B31" t="n">
-        <v>88998</v>
+        <v>89001</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3858,10 +3858,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129561598</v>
+        <v>129561826</v>
       </c>
       <c r="B32" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560048</v>
+        <v>560071</v>
       </c>
       <c r="R32" t="n">
-        <v>7063683</v>
+        <v>7063709</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3955,10 +3955,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129561392</v>
+        <v>129561598</v>
       </c>
       <c r="B33" t="n">
-        <v>91897</v>
+        <v>91602</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3966,21 +3966,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3990,10 +3990,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560043</v>
+        <v>560048</v>
       </c>
       <c r="R33" t="n">
-        <v>7063681</v>
+        <v>7063683</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4052,10 +4052,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129561840</v>
+        <v>129561392</v>
       </c>
       <c r="B34" t="n">
-        <v>91897</v>
+        <v>91900</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4087,10 +4087,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560074</v>
+        <v>560043</v>
       </c>
       <c r="R34" t="n">
-        <v>7063724</v>
+        <v>7063681</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4149,10 +4149,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129561826</v>
+        <v>129561840</v>
       </c>
       <c r="B35" t="n">
-        <v>91599</v>
+        <v>91900</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4160,21 +4160,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560071</v>
+        <v>560074</v>
       </c>
       <c r="R35" t="n">
-        <v>7063709</v>
+        <v>7063724</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4249,7 +4249,7 @@
         <v>129561747</v>
       </c>
       <c r="B36" t="n">
-        <v>83052</v>
+        <v>83055</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>129561089</v>
       </c>
       <c r="B37" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>129561632</v>
       </c>
       <c r="B38" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>129561809</v>
       </c>
       <c r="B39" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>129559867</v>
       </c>
       <c r="B40" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>129561092</v>
       </c>
       <c r="B41" t="n">
-        <v>91897</v>
+        <v>91900</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>129562162</v>
       </c>
       <c r="B42" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>129562154</v>
       </c>
       <c r="B43" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 32793-2025 artfynd.xlsx
+++ b/artfynd/A 32793-2025 artfynd.xlsx
@@ -3858,10 +3858,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129561826</v>
+        <v>129561392</v>
       </c>
       <c r="B32" t="n">
-        <v>91602</v>
+        <v>91900</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3869,21 +3869,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560071</v>
+        <v>560043</v>
       </c>
       <c r="R32" t="n">
-        <v>7063709</v>
+        <v>7063681</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3955,10 +3955,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129561598</v>
+        <v>129561840</v>
       </c>
       <c r="B33" t="n">
-        <v>91602</v>
+        <v>91900</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3966,21 +3966,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3990,10 +3990,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560048</v>
+        <v>560074</v>
       </c>
       <c r="R33" t="n">
-        <v>7063683</v>
+        <v>7063724</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4052,10 +4052,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129561392</v>
+        <v>129561826</v>
       </c>
       <c r="B34" t="n">
-        <v>91900</v>
+        <v>91602</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4063,21 +4063,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4087,10 +4087,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560043</v>
+        <v>560071</v>
       </c>
       <c r="R34" t="n">
-        <v>7063681</v>
+        <v>7063709</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4149,10 +4149,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129561840</v>
+        <v>129561598</v>
       </c>
       <c r="B35" t="n">
-        <v>91900</v>
+        <v>91602</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4160,21 +4160,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560074</v>
+        <v>560048</v>
       </c>
       <c r="R35" t="n">
-        <v>7063724</v>
+        <v>7063683</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
